--- a/data_lake/macro/Europe/CPI.xlsx
+++ b/data_lake/macro/Europe/CPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510DD307-2334-427C-A4CE-B00573C0E5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF487828-713D-40B1-ACAB-96CE4EFEFB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data_lake/macro/Europe/CPI.xlsx
+++ b/data_lake/macro/Europe/CPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF487828-713D-40B1-ACAB-96CE4EFEFB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B7AA0A-DF6D-47F0-953B-3EF6C7EA384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPICEMU" sheetId="1" r:id="rId1"/>
@@ -494,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H642"/>
+  <dimension ref="A1:H648"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="15" bestFit="1" customWidth="1"/>
@@ -15715,6 +15715,169 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="H642" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A643" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B643" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C643" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D643" s="11" t="str">
+        <f t="shared" ref="D643:D648" si="10">IF(
+ AND(
+  B643 &gt;= EOMONTH(DATE(YEAR(B643),3,1),0)
+        - WEEKDAY(EOMONTH(DATE(YEAR(B643),3,1),0),1)
+        + 1
+        + TIME(2,0,0),
+  B643 &lt; EOMONTH(DATE(YEAR(B643),10,1),0)
+       - WEEKDAY(EOMONTH(DATE(YEAR(B643),10,1),0),1)
+       + 1
+       + TIME(3,0,0)
+ ),
+ "UTC+2",
+ "UTC+1"
+)</f>
+        <v>UTC+2</v>
+      </c>
+      <c r="E643" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="F643" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="G643" s="13">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A644" s="9">
+        <v>46143</v>
+      </c>
+      <c r="B644" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C644" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D644" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E644" s="13">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F644" s="13">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G644" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="H644" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A645" s="9">
+        <v>46143</v>
+      </c>
+      <c r="B645" s="10">
+        <v>46190</v>
+      </c>
+      <c r="C645" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D645" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E645" s="13">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F645" s="13">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G645" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A646" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B646" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C646" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D646" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E646" s="13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F646" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="G646" s="13">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H646" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A647" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B647" s="10">
+        <v>46220</v>
+      </c>
+      <c r="C647" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D647" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E647" s="13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F647" s="13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G647" s="13">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A648" s="9">
+        <v>46204</v>
+      </c>
+      <c r="B648" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C648" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D648" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="F648" s="13">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G648" s="13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H648" s="14">
         <v>1</v>
       </c>
     </row>

--- a/data_lake/macro/Europe/CPI.xlsx
+++ b/data_lake/macro/Europe/CPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Europe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B7AA0A-DF6D-47F0-953B-3EF6C7EA384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE3CBA6-9071-4648-BA84-1B4FF0707F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPICEMU" sheetId="1" r:id="rId1"/>
@@ -494,13 +494,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H648"/>
+  <dimension ref="A1:H650"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.09765625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.69921875" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.59765625" style="13" bestFit="1" customWidth="1"/>
@@ -15729,7 +15729,7 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="D643" s="11" t="str">
-        <f t="shared" ref="D643:D648" si="10">IF(
+        <f t="shared" ref="D643:D650" si="10">IF(
  AND(
   B643 &gt;= EOMONTH(DATE(YEAR(B643),3,1),0)
         - WEEKDAY(EOMONTH(DATE(YEAR(B643),3,1),0),1)
@@ -15871,6 +15871,9 @@
         <f t="shared" si="10"/>
         <v>UTC+2</v>
       </c>
+      <c r="E648" s="13">
+        <v>2.9000000000000001E-2</v>
+      </c>
       <c r="F648" s="13">
         <v>2.9000000000000001E-2</v>
       </c>
@@ -15878,6 +15881,48 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="H648" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A649" s="9">
+        <v>46204</v>
+      </c>
+      <c r="B649" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C649" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D649" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="F649" s="13">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G649" s="13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A650" s="9">
+        <v>46235</v>
+      </c>
+      <c r="B650" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C650" s="11">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D650" s="11" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="G650" s="13">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H650" s="14">
         <v>1</v>
       </c>
     </row>
